--- a/tasks/finalpool/howtocook-scholarly-health-study/groundtruth_workspace/Health_Diet_Analysis.xlsx
+++ b/tasks/finalpool/howtocook-scholarly-health-study/groundtruth_workspace/Health_Diet_Analysis.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Dish Name</t>
+          <t>Dish_Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -431,17 +431,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ingredient Count</t>
+          <t>Estimated_Calories</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Protein_g</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Key Ingredients</t>
+          <t>Fat_g</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Carbs_g</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Health_Rating</t>
         </is>
       </c>
     </row>
@@ -457,14 +467,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>鸡翅, 可乐, 生抽, 老抽, 料酒, 姜, 蒜, 葱, 盐</t>
+        <v>26</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -480,83 +496,107 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>480</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>鱼片, 豆芽, 花椒, 干辣椒, 郫县豆瓣酱, 姜, 蒜, 料酒, 淀粉</t>
+        <v>32</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>凉拌金针菇</t>
+          <t>扬州炒饭</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>素菜</t>
+          <t>主食</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>600</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>金针菇, 蒜, 辣椒油, 醋, 生抽, 香油, 糖, 盐</t>
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>炒年糕</t>
+          <t>紫菜蛋花汤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主食</t>
+          <t>汤</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>年糕, 白菜, 胡萝卜, 甜辣酱, 酱油</t>
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>奶油蘑菇汤</t>
+          <t>凉拌金针菇</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>汤</t>
+          <t>素菜</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>蘑菇, 黄油, 洋葱, 面粉, 牛奶, 淡奶油, 盐, 胡椒粉, 百里香</t>
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -571,13 +611,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Paper Title</t>
+          <t>Paper_Title</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -587,92 +627,109 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Citation Count</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Relevance Notes</t>
+          <t>Citation_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Key_Finding</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A Survey on Attention Mechanisms in Deep Learning</t>
+          <t>Dietary Patterns and Risk of Chronic Disease</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wei Lin, Sarah Johnson, Tao Wang</t>
+          <t>Sarah Johnson, Michael Brown, Lisa Wang, David Kim</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>245</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Chain-of-thought reasoning methods could be applied to multi-step nutritional analysis of complex recipes.</t>
+        <v>2020</v>
+      </c>
+      <c r="D2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Diets rich in whole grains, fruits, vegetables and lean proteins are associated with reduced chronic disease risk.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vision-Language Pretraining with Cross-Modal Transformers</t>
+          <t>Mediterranean Diet and Cardiovascular Health</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jennifer Lee, Raj Patel, Chris Anderson</t>
+          <t>Maria Garcia, Antonio Romano, Elena Costa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>156</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Self-consistency techniques can validate nutritional calculations across different estimation methods.</t>
+        <v>2020</v>
+      </c>
+      <c r="D3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Meta-analysis of 23 randomized controlled trials shows reduced cardiovascular events, blood pressure and inflammatory markers.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mixed Precision Training of Deep Neural Networks: Methods and Best Practices</t>
+          <t>Plant-Based Diets: A Review of Evidence</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yuki Sato, Andreas Muller</t>
+          <t>James Chen, Rachel Green, Thomas Liu</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tree of thoughts framework enables systematic exploration of ingredient substitution options for healthier recipes.</t>
+        <v>2021</v>
+      </c>
+      <c r="D4" t="n">
+        <v>350</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Well-planned plant-based diets are nutritionally adequate and beneficial for disease prevention.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Climate Change Impact on Coastal Erosion Patterns</t>
+          <t>Machine Learning for Drug Discovery</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maria Costa</t>
+          <t>Alex Zhang, Jennifer Wu</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mathematical reasoning approaches can be used to compute precise nutritional breakdowns from ingredient quantities.</t>
+        <v>2021</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Deep learning accelerates molecular property prediction and de novo drug design.</t>
         </is>
       </c>
     </row>
@@ -687,71 +744,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Metric Name</t>
+          <t>Dish_Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Health_Rating</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Supporting_Research</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total Recipes Analyzed</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
+          <t>可乐鸡翅</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mediterranean Diet and Cardiovascular Health: balanced protein intake aligns with cardiovascular benefits.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Average Ingredient Count</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8</v>
+          <t>水煮鱼</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dietary Patterns and Risk of Chronic Disease: seafood-rich dietary patterns are linked to lower chronic disease risk.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Most Common Category</t>
+          <t>扬州炒饭</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>荤菜</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dietary Patterns and Risk of Chronic Disease and Plant-Based Diets: balance staple carbohydrates with protein and vegetables.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total Research References</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+          <t>紫菜蛋花汤</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dietary Patterns and Risk of Chronic Disease: low-calorie soups support weight management.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total Combined Citations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>557</v>
+          <t>凉拌金针菇</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Plant-Based Diets: A Review of Evidence: vegetable and mushroom dishes support plant-based dietary patterns.</t>
+        </is>
       </c>
     </row>
   </sheetData>
